--- a/data/trans_orig/IP1015-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP1015-Provincia-trans_orig.xlsx
@@ -1801,7 +1801,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3332</t>
+          <t>3893</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1836,7 +1836,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4015</t>
+          <t>3418</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,22%</t>
         </is>
       </c>
     </row>
@@ -1909,7 +1909,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>75779</t>
+          <t>75218</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1924,7 +1924,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,79%</t>
+          <t>95,08%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1944,7 +1944,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>149957</t>
+          <t>150554</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -3173,7 +3173,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>4678</t>
+          <t>4868</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3188,7 +3188,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3208,7 +3208,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4320</t>
+          <t>4213</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3223,7 +3223,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,31%</t>
         </is>
       </c>
     </row>
@@ -3281,7 +3281,7 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>159380</t>
+          <t>159190</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>97,03%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3316,7 +3316,7 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>317642</t>
+          <t>317749</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,69%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3511,12 +3511,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>673</t>
+          <t>674</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>5550</t>
+          <t>5775</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>672</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>6233</t>
+          <t>5532</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3561,12 +3561,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,39%</t>
         </is>
       </c>
     </row>
@@ -3624,12 +3624,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>717150</t>
+          <t>716925</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>722027</t>
+          <t>722026</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3639,7 +3639,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,2%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3659,12 +3659,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1397488</t>
+          <t>1398189</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1403049</t>
+          <t>1403721</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3674,12 +3674,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,61%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>99,95%</t>
+          <t>100,0%</t>
         </is>
       </c>
     </row>
@@ -4060,7 +4060,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3181</t>
+          <t>2634</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4075,7 +4075,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4130,7 +4130,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>2756</t>
+          <t>2473</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4145,7 +4145,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,17%</t>
         </is>
       </c>
     </row>
@@ -4168,7 +4168,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>49783</t>
+          <t>50330</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -4183,7 +4183,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,99%</t>
+          <t>95,03%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -4238,7 +4238,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>110969</t>
+          <t>111252</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -4253,7 +4253,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,83%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4438,7 +4438,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3082</t>
+          <t>3528</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4453,7 +4453,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4473,7 +4473,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>2802</t>
+          <t>3050</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4488,7 +4488,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,41%</t>
         </is>
       </c>
     </row>
@@ -4546,7 +4546,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>108077</t>
+          <t>107631</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -4561,7 +4561,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>96,83%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>213070</t>
+          <t>212822</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,59%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -5810,7 +5810,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3527</t>
+          <t>3511</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5825,7 +5825,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5845,7 +5845,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>3451</t>
+          <t>3476</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5860,7 +5860,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,99%</t>
         </is>
       </c>
     </row>
@@ -5918,7 +5918,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>56718</t>
+          <t>56734</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -5933,7 +5933,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>94,15%</t>
+          <t>94,17%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -5953,7 +5953,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>112779</t>
+          <t>112754</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -5968,7 +5968,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>97,01%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -6496,7 +6496,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>4474</t>
+          <t>3761</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6511,7 +6511,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6531,7 +6531,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4287</t>
+          <t>4039</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6546,7 +6546,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,2%</t>
         </is>
       </c>
     </row>
@@ -6604,7 +6604,7 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>166841</t>
+          <t>167554</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
@@ -6619,7 +6619,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -6639,7 +6639,7 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>331736</t>
+          <t>331984</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
@@ -6654,7 +6654,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,8%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -6804,7 +6804,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>2169</t>
+          <t>2397</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6819,7 +6819,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6834,12 +6834,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>606</t>
+          <t>604</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>5701</t>
+          <t>5543</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6854,7 +6854,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6869,12 +6869,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>685</t>
+          <t>687</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>6167</t>
+          <t>6259</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6889,7 +6889,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,43%</t>
         </is>
       </c>
     </row>
@@ -6912,7 +6912,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>704759</t>
+          <t>704531</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -6927,7 +6927,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>99,69%</t>
+          <t>99,66%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -6947,12 +6947,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>742441</t>
+          <t>742599</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>747536</t>
+          <t>747538</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6962,7 +6962,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -6982,12 +6982,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1448903</t>
+          <t>1448811</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1454385</t>
+          <t>1454383</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6997,7 +6997,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>99,57%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -8104,7 +8104,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4327</t>
+          <t>3596</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8119,7 +8119,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8139,7 +8139,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3608</t>
+          <t>3843</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8154,7 +8154,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,81%</t>
         </is>
       </c>
     </row>
@@ -8212,7 +8212,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>65578</t>
+          <t>66309</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -8227,7 +8227,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,81%</t>
+          <t>94,86%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -8247,7 +8247,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>133128</t>
+          <t>132893</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -8262,7 +8262,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>97,19%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -9476,7 +9476,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3262</t>
+          <t>3264</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9491,7 +9491,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9511,7 +9511,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3253</t>
+          <t>3871</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9526,7 +9526,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,38%</t>
         </is>
       </c>
     </row>
@@ -9584,7 +9584,7 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>140810</t>
+          <t>140808</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
@@ -9599,7 +9599,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,73%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -9619,7 +9619,7 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>278193</t>
+          <t>277575</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
@@ -9634,7 +9634,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,62%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -10162,7 +10162,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>4223</t>
+          <t>4777</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10177,7 +10177,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10197,7 +10197,7 @@
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>4769</t>
+          <t>4180</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10212,7 +10212,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,29%</t>
         </is>
       </c>
     </row>
@@ -10270,7 +10270,7 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>740621</t>
+          <t>740067</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
@@ -10285,7 +10285,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,36%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -10305,7 +10305,7 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1444446</t>
+          <t>1445035</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
@@ -10320,7 +10320,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>99,67%</t>
+          <t>99,71%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">

--- a/data/trans_orig/IP1015-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP1015-Provincia-trans_orig.xlsx
@@ -543,7 +543,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -840,42 +840,42 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
+          <t>60217</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
           <t>52568</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>60217</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -953,52 +953,52 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
+          <t>60217</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>60217</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>60217</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
           <t>52568</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>52568</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>52568</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>60217</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>60217</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>60217</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1178,47 +1178,47 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>108757</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>156</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>101562</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>164</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>108757</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -1291,57 +1291,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>108757</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>108757</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>108757</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>156</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>101562</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>101562</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>101562</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>164</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>108757</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>108757</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>108757</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1521,47 +1521,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>70327</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>93</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>67597</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>113</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>70327</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1634,57 +1634,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>70327</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>70327</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>70327</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>93</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>67597</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>67597</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>67597</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>113</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>70327</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>70327</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>70327</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1751,107 +1751,107 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>673</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3366</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
+          <t>0,85%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="R13" s="2" t="inlineStr">
         <is>
           <t>673</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>3893</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,85%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>3367</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>0,44%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>4,92%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>673</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>3418</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,44%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,19%</t>
         </is>
       </c>
     </row>
@@ -1864,72 +1864,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>78438</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>75745</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>79111</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>99,15%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>95,75%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>114</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>74861</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>115</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>78438</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>75218</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>79111</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>99,15%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,08%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,7 +1944,7 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>150554</t>
+          <t>150605</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,81%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -1977,57 +1977,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>79111</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>79111</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>79111</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>114</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>74861</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>74861</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>74861</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>79111</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>79111</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>79111</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2207,47 +2207,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>44843</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>61</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>41852</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>44843</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -2320,57 +2320,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>44843</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>44843</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>44843</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>61</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>41852</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>41852</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>41852</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>44843</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>44843</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>44843</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2550,47 +2550,47 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>59732</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>82</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>56055</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>59732</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -2663,57 +2663,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>59732</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>59732</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>59732</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>82</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>56055</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>56055</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>56055</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>59732</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>59732</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>59732</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2893,47 +2893,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>197</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>135655</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>186</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>128622</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>197</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>135655</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
@@ -3006,57 +3006,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>197</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>135655</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>135655</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>135655</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>186</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>128622</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>128622</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>128622</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>197</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>135655</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>135655</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>135655</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3123,107 +3123,107 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1401</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4357</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
+          <t>0,85%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K25" s="2" t="inlineStr">
+      <c r="R25" s="2" t="inlineStr">
         <is>
           <t>1401</t>
         </is>
       </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>4868</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>0,85%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>4937</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>0,44%</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>2,97%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>1401</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>4213</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>0,44%</t>
-        </is>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,53%</t>
         </is>
       </c>
     </row>
@@ -3236,72 +3236,72 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>251</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>162657</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>159701</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>164058</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>99,15%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>97,34%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>241</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
         <is>
           <t>157904</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>251</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>162657</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>159190</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>164058</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>99,15%</t>
-        </is>
-      </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3316,7 +3316,7 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>317749</t>
+          <t>317025</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,47%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3349,57 +3349,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>253</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>164058</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>164058</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>164058</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>241</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
         <is>
           <t>157904</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="L27" s="2" t="inlineStr">
         <is>
           <t>157904</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="M27" s="2" t="inlineStr">
         <is>
           <t>157904</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>253</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>164058</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>164058</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>164058</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3466,92 +3466,92 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2074</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>672</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5534</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
+          <t>0,29%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>0,09%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>0,77%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="K28" s="2" t="inlineStr">
+      <c r="R28" s="2" t="inlineStr">
         <is>
           <t>2074</t>
         </is>
       </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>674</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>5775</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>0,29%</t>
-        </is>
-      </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t>0,09%</t>
-        </is>
-      </c>
-      <c r="P28" s="2" t="inlineStr">
-        <is>
-          <t>0,8%</t>
-        </is>
-      </c>
-      <c r="Q28" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R28" s="2" t="inlineStr">
-        <is>
-          <t>2074</t>
-        </is>
-      </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>672</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>5532</t>
+          <t>5560</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3561,12 +3561,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,05%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,4%</t>
         </is>
       </c>
     </row>
@@ -3579,72 +3579,72 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>1083</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>720626</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>717166</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>722028</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>99,71%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>99,23%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>99,91%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>1018</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="K29" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>1083</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>720626</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>716925</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>722026</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>99,71%</t>
-        </is>
-      </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>99,91%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3659,12 +3659,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1398189</t>
+          <t>1398161</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1403721</t>
+          <t>1403049</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3674,12 +3674,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>99,61%</t>
+          <t>99,6%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>99,95%</t>
         </is>
       </c>
     </row>
@@ -3692,57 +3692,57 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>1086</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>1018</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="K30" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="L30" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="M30" s="2" t="inlineStr">
         <is>
           <t>681021</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>1086</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3866,7 +3866,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3877,7 +3877,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4045,107 +4045,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>480</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2634</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>2421</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,91%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>4,97%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>4,57%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>480</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>2965</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,42%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>480</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>2473</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,42%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,61%</t>
         </is>
       </c>
     </row>
@@ -4158,74 +4158,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>60761</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>80</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>52484</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>50330</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>50543</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>52964</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>99,09%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>95,03%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>95,43%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>60761</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>163</t>
@@ -4238,7 +4238,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>111252</t>
+          <t>110760</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -4253,7 +4253,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,39%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4271,57 +4271,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>60761</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>60761</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>60761</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>81</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>52964</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>52964</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>52964</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>60761</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>60761</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>60761</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4388,107 +4388,107 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>607</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3096</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
+          <t>0,55%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="R7" s="2" t="inlineStr">
         <is>
           <t>607</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>3528</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,55%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>3020</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>0,28%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>3,17%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>607</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>3050</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,28%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,4%</t>
         </is>
       </c>
     </row>
@@ -4501,72 +4501,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>110552</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>108063</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>111159</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>99,45%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>97,21%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>152</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>104713</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>164</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>110552</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>107631</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>111159</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>99,45%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>212822</t>
+          <t>212852</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,6%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4614,57 +4614,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>111159</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>111159</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>111159</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>152</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>104713</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>104713</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>104713</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>165</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>111159</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>111159</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>111159</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4844,47 +4844,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>70584</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>94</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>68178</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>70584</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -4957,57 +4957,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>70584</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>70584</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>70584</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>94</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>68178</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>68178</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>68178</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>101</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>70584</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>70584</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>70584</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5187,47 +5187,47 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>82234</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>114</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>77761</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>112</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>82234</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -5300,57 +5300,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>82234</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>82234</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>82234</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>114</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>77761</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>77761</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>77761</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>112</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>82234</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>82234</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>82234</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5530,47 +5530,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>46105</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>58</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>43901</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>46105</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -5643,57 +5643,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>46105</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>46105</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>46105</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>58</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>43901</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>43901</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>43901</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>46105</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>46105</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>46105</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5760,107 +5760,107 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>687</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3547</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
+          <t>1,14%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
+      <c r="R19" s="2" t="inlineStr">
         <is>
           <t>687</t>
         </is>
       </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>3511</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>1,14%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>3439</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>0,59%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>5,83%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>687</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>3476</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>0,59%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,96%</t>
         </is>
       </c>
     </row>
@@ -5873,72 +5873,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>59558</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>56698</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>60245</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>98,86%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>94,11%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>79</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>55985</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>59558</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>56734</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>60245</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>98,86%</t>
-        </is>
-      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>94,17%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5953,7 +5953,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>112754</t>
+          <t>112791</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -5968,7 +5968,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>97,04%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -5986,57 +5986,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>60245</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>60245</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>60245</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>79</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>55985</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>55985</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>55985</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>60245</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>60245</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>60245</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6216,47 +6216,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>207</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>145739</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>193</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>138718</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>207</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>145739</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
@@ -6329,57 +6329,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>207</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>145739</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>145739</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>145739</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>193</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>138718</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>138718</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>138718</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>207</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>145739</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>145739</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>145739</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6446,107 +6446,107 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>747</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3706</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
+          <t>0,44%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K25" s="2" t="inlineStr">
+      <c r="R25" s="2" t="inlineStr">
         <is>
           <t>747</t>
         </is>
       </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>3761</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>0,44%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>3752</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>0,22%</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>2,2%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>747</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>4039</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>0,22%</t>
-        </is>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,12%</t>
         </is>
       </c>
     </row>
@@ -6559,72 +6559,72 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>170568</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>167609</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>171315</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>99,56%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>97,84%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>247</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
         <is>
           <t>164708</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>170568</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>167554</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>171315</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>99,56%</t>
-        </is>
-      </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6639,7 +6639,7 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>331984</t>
+          <t>332271</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
@@ -6654,7 +6654,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,88%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -6672,57 +6672,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>251</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>171315</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>171315</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>171315</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>247</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
         <is>
           <t>164708</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="L27" s="2" t="inlineStr">
         <is>
           <t>164708</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="M27" s="2" t="inlineStr">
         <is>
           <t>164708</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>251</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>171315</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>171315</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>171315</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -6789,74 +6789,74 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>2041</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>607</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>5434</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>0,27%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>0,08%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>0,73%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="K28" s="2" t="inlineStr">
         <is>
           <t>480</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>2397</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>2419</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
         <is>
           <t>0,07%</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="O28" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr">
+      <c r="P28" s="2" t="inlineStr">
         <is>
           <t>0,34%</t>
         </is>
       </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>2041</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>604</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>5543</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>0,27%</t>
-        </is>
-      </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t>0,08%</t>
-        </is>
-      </c>
-      <c r="P28" s="2" t="inlineStr">
-        <is>
-          <t>0,74%</t>
-        </is>
-      </c>
       <c r="Q28" s="2" t="inlineStr">
         <is>
           <t>4</t>
@@ -6869,12 +6869,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>687</t>
+          <t>683</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>6259</t>
+          <t>6410</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6889,7 +6889,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,44%</t>
         </is>
       </c>
     </row>
@@ -6902,74 +6902,74 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>1063</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>746101</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>742708</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>747535</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>99,73%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>99,27%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>99,92%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>1017</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="K29" s="2" t="inlineStr">
         <is>
           <t>706448</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>704531</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>704509</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
         <is>
           <t>706928</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="N29" s="2" t="inlineStr">
         <is>
           <t>99,93%</t>
         </is>
       </c>
-      <c r="H29" s="2" t="inlineStr">
+      <c r="O29" s="2" t="inlineStr">
         <is>
           <t>99,66%</t>
         </is>
       </c>
-      <c r="I29" s="2" t="inlineStr">
+      <c r="P29" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>1063</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>746101</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>742599</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>747538</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>99,73%</t>
-        </is>
-      </c>
-      <c r="O29" s="2" t="inlineStr">
-        <is>
-          <t>99,26%</t>
-        </is>
-      </c>
-      <c r="P29" s="2" t="inlineStr">
-        <is>
-          <t>99,92%</t>
-        </is>
-      </c>
       <c r="Q29" s="2" t="inlineStr">
         <is>
           <t>2080</t>
@@ -6982,12 +6982,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1448811</t>
+          <t>1448660</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1454383</t>
+          <t>1454387</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6997,7 +6997,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>99,56%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -7015,57 +7015,57 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>1066</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>748142</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>748142</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>748142</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>1018</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="K30" s="2" t="inlineStr">
         <is>
           <t>706928</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="L30" s="2" t="inlineStr">
         <is>
           <t>706928</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="M30" s="2" t="inlineStr">
         <is>
           <t>706928</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>1066</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>748142</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t>748142</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>748142</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7189,7 +7189,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -7200,7 +7200,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -7481,47 +7481,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>64462</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>93</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>57371</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>64462</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -7594,57 +7594,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>64462</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>64462</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>64462</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>93</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>57371</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>57371</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>57371</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>64462</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>64462</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>64462</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7824,47 +7824,47 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>110283</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>157</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>103947</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>161</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>110283</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -7937,57 +7937,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>110283</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>110283</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>110283</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>157</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>103947</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>103947</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>103947</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>161</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>110283</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>110283</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>110283</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8054,107 +8054,107 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>718</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3617</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
+          <t>1,03%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="R10" s="2" t="inlineStr">
         <is>
           <t>718</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>3596</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>1,03%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>3612</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>0,53%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>5,14%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>718</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>3843</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,53%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,64%</t>
         </is>
       </c>
     </row>
@@ -8167,72 +8167,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>69187</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>66288</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>69905</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>98,97%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>94,83%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>89</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>66831</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>69187</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>66309</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>69905</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>98,97%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,86%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8247,7 +8247,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>132893</t>
+          <t>133124</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -8262,7 +8262,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>97,36%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -8280,57 +8280,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>69905</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>69905</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>69905</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>89</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>66831</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>66831</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>66831</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>69905</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>69905</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>69905</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8510,47 +8510,47 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>81184</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>112</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>76961</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>81184</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -8623,57 +8623,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>81184</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>81184</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>81184</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>112</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>76961</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>76961</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>76961</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>81184</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>81184</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>81184</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8853,47 +8853,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>46350</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>63</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>43438</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>46350</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -8966,57 +8966,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>46350</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>46350</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>46350</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>63</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>43438</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>43438</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>43438</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>46350</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>46350</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>46350</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9196,47 +9196,47 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>57739</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>79</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>54273</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>57739</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -9309,57 +9309,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>57739</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>57739</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>57739</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>79</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>54273</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>54273</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>54273</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>57739</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>57739</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>57739</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -9426,107 +9426,107 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>646</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2955</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
+          <t>0,45%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K22" s="2" t="inlineStr">
+      <c r="R22" s="2" t="inlineStr">
         <is>
           <t>646</t>
         </is>
       </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>3264</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>0,45%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>3249</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>0,23%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>2,27%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>646</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>3871</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>0,23%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,15%</t>
         </is>
       </c>
     </row>
@@ -9544,67 +9544,67 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
+          <t>143426</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>141117</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>144072</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>99,55%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>97,95%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>207</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
           <t>137374</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>207</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>143426</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>140808</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>144072</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>99,55%</t>
-        </is>
-      </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9619,7 +9619,7 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>277575</t>
+          <t>278197</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
@@ -9634,7 +9634,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -9652,57 +9652,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>208</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>144072</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>144072</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>144072</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>207</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>137374</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>137374</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>137374</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>208</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>144072</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>144072</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>144072</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9882,47 +9882,47 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>255</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>170849</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>261</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
         <is>
           <t>164176</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>255</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>170849</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
@@ -9995,57 +9995,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>255</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>170849</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>170849</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>170849</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>261</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
         <is>
           <t>164176</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="L27" s="2" t="inlineStr">
         <is>
           <t>164176</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="M27" s="2" t="inlineStr">
         <is>
           <t>164176</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>255</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>170849</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>170849</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>170849</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -10112,107 +10112,107 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1364</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4836</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
+          <t>0,18%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K28" s="2" t="inlineStr">
+      <c r="R28" s="2" t="inlineStr">
         <is>
           <t>1364</t>
         </is>
       </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>4777</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>0,18%</t>
-        </is>
-      </c>
-      <c r="O28" s="2" t="inlineStr">
+      <c r="S28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T28" s="2" t="inlineStr">
+        <is>
+          <t>4926</t>
+        </is>
+      </c>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>0,09%</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P28" s="2" t="inlineStr">
-        <is>
-          <t>0,64%</t>
-        </is>
-      </c>
-      <c r="Q28" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R28" s="2" t="inlineStr">
-        <is>
-          <t>1364</t>
-        </is>
-      </c>
-      <c r="S28" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T28" s="2" t="inlineStr">
-        <is>
-          <t>4180</t>
-        </is>
-      </c>
-      <c r="U28" s="2" t="inlineStr">
-        <is>
-          <t>0,09%</t>
-        </is>
-      </c>
-      <c r="V28" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,34%</t>
         </is>
       </c>
     </row>
@@ -10225,72 +10225,72 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>1063</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>743480</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>740008</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>99,82%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>99,35%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>1061</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="K29" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>1063</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>743480</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>740067</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>99,82%</t>
-        </is>
-      </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10305,7 +10305,7 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1445035</t>
+          <t>1444289</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
@@ -10320,7 +10320,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>99,66%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -10338,57 +10338,57 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>1065</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>1061</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="K30" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="L30" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="M30" s="2" t="inlineStr">
         <is>
           <t>704371</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>1065</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
